--- a/Team-Data/2014-15/4-8-2014-15.xlsx
+++ b/Team-Data/2014-15/4-8-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F2" t="n">
         <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>0.756</v>
+        <v>0.753</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J2" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.468</v>
+        <v>0.467</v>
       </c>
       <c r="L2" t="n">
         <v>10</v>
@@ -700,7 +767,7 @@
         <v>21.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.778</v>
+        <v>0.779</v>
       </c>
       <c r="R2" t="n">
         <v>8.699999999999999</v>
@@ -712,10 +779,10 @@
         <v>40.6</v>
       </c>
       <c r="U2" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="V2" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W2" t="n">
         <v>9</v>
@@ -733,13 +800,13 @@
         <v>19.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.7</v>
+        <v>102.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -754,7 +821,7 @@
         <v>26</v>
       </c>
       <c r="AI2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ2" t="n">
         <v>27</v>
@@ -778,7 +845,7 @@
         <v>24</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
         <v>30</v>
@@ -799,10 +866,10 @@
         <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ2" t="n">
         <v>1</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -843,25 +910,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
         <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>0.462</v>
+        <v>0.455</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="J3" t="n">
-        <v>87.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="K3" t="n">
         <v>0.442</v>
@@ -870,34 +937,34 @@
         <v>8</v>
       </c>
       <c r="M3" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="N3" t="n">
         <v>0.325</v>
       </c>
       <c r="O3" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="P3" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.757</v>
+        <v>0.752</v>
       </c>
       <c r="R3" t="n">
         <v>11.1</v>
       </c>
       <c r="S3" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T3" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="U3" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="V3" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W3" t="n">
         <v>8</v>
@@ -909,28 +976,28 @@
         <v>5.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.2</v>
+        <v>101.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
         <v>7</v>
@@ -960,7 +1027,7 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
         <v>11</v>
@@ -969,7 +1036,7 @@
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
         <v>5</v>
@@ -978,19 +1045,19 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX3" t="n">
         <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB3" t="n">
         <v>12</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E4" t="n">
         <v>36</v>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>0.462</v>
+        <v>0.468</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1043,28 +1110,28 @@
         <v>37.5</v>
       </c>
       <c r="J4" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L4" t="n">
         <v>6.6</v>
       </c>
       <c r="M4" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
       <c r="O4" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P4" t="n">
         <v>22.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.75</v>
+        <v>0.748</v>
       </c>
       <c r="R4" t="n">
         <v>10.2</v>
@@ -1073,7 +1140,7 @@
         <v>32</v>
       </c>
       <c r="T4" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U4" t="n">
         <v>20.9</v>
@@ -1097,13 +1164,13 @@
         <v>20</v>
       </c>
       <c r="AB4" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC4" t="n">
         <v>-3</v>
       </c>
       <c r="AD4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE4" t="n">
         <v>17</v>
@@ -1115,7 +1182,7 @@
         <v>17</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
         <v>16</v>
@@ -1124,7 +1191,7 @@
         <v>17</v>
       </c>
       <c r="AK4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
         <v>24</v>
@@ -1136,10 +1203,10 @@
         <v>26</v>
       </c>
       <c r="AO4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP4" t="n">
         <v>18</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>19</v>
       </c>
       <c r="AQ4" t="n">
         <v>20</v>
@@ -1148,7 +1215,7 @@
         <v>24</v>
       </c>
       <c r="AS4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT4" t="n">
         <v>22</v>
@@ -1157,7 +1224,7 @@
         <v>20</v>
       </c>
       <c r="AV4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
         <v>24</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -1207,43 +1274,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E5" t="n">
         <v>33</v>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>0.423</v>
+        <v>0.429</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J5" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.422</v>
+        <v>0.423</v>
       </c>
       <c r="L5" t="n">
         <v>5.9</v>
       </c>
       <c r="M5" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.317</v>
+        <v>0.315</v>
       </c>
       <c r="O5" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P5" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="Q5" t="n">
         <v>0.751</v>
@@ -1252,16 +1319,16 @@
         <v>10.1</v>
       </c>
       <c r="S5" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="T5" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="U5" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V5" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="W5" t="n">
         <v>6</v>
@@ -1270,22 +1337,22 @@
         <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.7</v>
+        <v>95</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1324,16 +1391,16 @@
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR5" t="n">
         <v>25</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU5" t="n">
         <v>26</v>
@@ -1348,7 +1415,7 @@
         <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ5" t="n">
         <v>5</v>
@@ -1357,7 +1424,7 @@
         <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E6" t="n">
         <v>46</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>0.59</v>
+        <v>0.597</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
@@ -1407,7 +1474,7 @@
         <v>36.6</v>
       </c>
       <c r="J6" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K6" t="n">
         <v>0.442</v>
@@ -1416,19 +1483,19 @@
         <v>7.8</v>
       </c>
       <c r="M6" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="N6" t="n">
-        <v>0.355</v>
+        <v>0.353</v>
       </c>
       <c r="O6" t="n">
         <v>19.8</v>
       </c>
       <c r="P6" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.784</v>
+        <v>0.785</v>
       </c>
       <c r="R6" t="n">
         <v>11.7</v>
@@ -1458,25 +1525,25 @@
         <v>18.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB6" t="n">
         <v>100.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH6" t="n">
         <v>7</v>
@@ -1485,10 +1552,10 @@
         <v>23</v>
       </c>
       <c r="AJ6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
@@ -1503,7 +1570,7 @@
         <v>2</v>
       </c>
       <c r="AP6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ6" t="n">
         <v>3</v>
@@ -1512,7 +1579,7 @@
         <v>7</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
         <v>3</v>
@@ -1521,7 +1588,7 @@
         <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
         <v>29</v>
@@ -1530,7 +1597,7 @@
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ6" t="n">
         <v>3</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
         <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>0.654</v>
+        <v>0.649</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
@@ -1589,7 +1656,7 @@
         <v>37.7</v>
       </c>
       <c r="J7" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K7" t="n">
         <v>0.459</v>
@@ -1598,7 +1665,7 @@
         <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="N7" t="n">
         <v>0.366</v>
@@ -1607,10 +1674,10 @@
         <v>18</v>
       </c>
       <c r="P7" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R7" t="n">
         <v>11.1</v>
@@ -1625,7 +1692,7 @@
         <v>21.9</v>
       </c>
       <c r="V7" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W7" t="n">
         <v>7.5</v>
@@ -1649,7 +1716,7 @@
         <v>5.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
@@ -1661,7 +1728,7 @@
         <v>7</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>14</v>
@@ -1682,16 +1749,16 @@
         <v>6</v>
       </c>
       <c r="AO7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP7" t="n">
         <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS7" t="n">
         <v>21</v>
@@ -1715,10 +1782,10 @@
         <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB7" t="n">
         <v>6</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -1756,22 +1823,22 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>0.61</v>
+        <v>0.597</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
       </c>
       <c r="I8" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J8" t="n">
-        <v>85.7</v>
+        <v>85.5</v>
       </c>
       <c r="K8" t="n">
         <v>0.461</v>
@@ -1780,13 +1847,13 @@
         <v>8.9</v>
       </c>
       <c r="M8" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.348</v>
+        <v>0.35</v>
       </c>
       <c r="O8" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P8" t="n">
         <v>22.3</v>
@@ -1795,13 +1862,13 @@
         <v>0.751</v>
       </c>
       <c r="R8" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="U8" t="n">
         <v>22.4</v>
@@ -1810,7 +1877,7 @@
         <v>12.9</v>
       </c>
       <c r="W8" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X8" t="n">
         <v>4.5</v>
@@ -1819,10 +1886,10 @@
         <v>3.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AB8" t="n">
         <v>104.6</v>
@@ -1831,7 +1898,7 @@
         <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1846,10 +1913,10 @@
         <v>15</v>
       </c>
       <c r="AI8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1864,22 +1931,22 @@
         <v>13</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP8" t="n">
         <v>17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR8" t="n">
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1888,7 +1955,7 @@
         <v>3</v>
       </c>
       <c r="AW8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX8" t="n">
         <v>21</v>
@@ -1906,7 +1973,7 @@
         <v>3</v>
       </c>
       <c r="BC8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -1935,37 +2002,37 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F9" t="n">
         <v>49</v>
       </c>
       <c r="G9" t="n">
-        <v>0.372</v>
+        <v>0.364</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J9" t="n">
-        <v>86.8</v>
+        <v>86.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0.431</v>
+        <v>0.43</v>
       </c>
       <c r="L9" t="n">
         <v>7.9</v>
       </c>
       <c r="M9" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.323</v>
+        <v>0.321</v>
       </c>
       <c r="O9" t="n">
         <v>17.6</v>
@@ -1974,7 +2041,7 @@
         <v>24.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.731</v>
+        <v>0.73</v>
       </c>
       <c r="R9" t="n">
         <v>12.1</v>
@@ -1986,7 +2053,7 @@
         <v>44.4</v>
       </c>
       <c r="U9" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V9" t="n">
         <v>14.1</v>
@@ -1998,7 +2065,7 @@
         <v>4.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z9" t="n">
         <v>22.8</v>
@@ -2007,13 +2074,13 @@
         <v>20.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>100.3</v>
+        <v>100.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>-3.7</v>
+        <v>-4</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2025,7 +2092,7 @@
         <v>24</v>
       </c>
       <c r="AH9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
         <v>18</v>
@@ -2052,16 +2119,16 @@
         <v>8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR9" t="n">
         <v>3</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AU9" t="n">
         <v>16</v>
@@ -2073,7 +2140,7 @@
         <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY9" t="n">
         <v>29</v>
@@ -2088,7 +2155,7 @@
         <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -2117,43 +2184,43 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E10" t="n">
         <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>0.385</v>
+        <v>0.39</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J10" t="n">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="K10" t="n">
-        <v>0.43</v>
+        <v>0.428</v>
       </c>
       <c r="L10" t="n">
         <v>8.4</v>
       </c>
       <c r="M10" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="N10" t="n">
         <v>0.338</v>
       </c>
       <c r="O10" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P10" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q10" t="n">
         <v>0.705</v>
@@ -2165,13 +2232,13 @@
         <v>32.1</v>
       </c>
       <c r="T10" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="U10" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V10" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W10" t="n">
         <v>7.6</v>
@@ -2180,22 +2247,22 @@
         <v>4.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>98.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.6</v>
+        <v>-1.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,13 +2274,13 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK10" t="n">
         <v>27</v>
@@ -2222,13 +2289,13 @@
         <v>11</v>
       </c>
       <c r="AM10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN10" t="n">
         <v>23</v>
       </c>
       <c r="AO10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP10" t="n">
         <v>16</v>
@@ -2258,10 +2325,10 @@
         <v>13</v>
       </c>
       <c r="AY10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>10.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2389,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
@@ -2416,7 +2483,7 @@
         <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR11" t="n">
         <v>20</v>
@@ -2437,7 +2504,7 @@
         <v>4</v>
       </c>
       <c r="AX11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -2484,22 +2551,22 @@
         <v>77</v>
       </c>
       <c r="E12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>0.675</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J12" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K12" t="n">
         <v>0.442</v>
@@ -2508,34 +2575,34 @@
         <v>11.5</v>
       </c>
       <c r="M12" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="N12" t="n">
         <v>0.347</v>
       </c>
       <c r="O12" t="n">
-        <v>17.9</v>
+        <v>18.2</v>
       </c>
       <c r="P12" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.719</v>
+        <v>0.718</v>
       </c>
       <c r="R12" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S12" t="n">
         <v>31.8</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U12" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V12" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="W12" t="n">
         <v>9.6</v>
@@ -2547,28 +2614,28 @@
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.5</v>
+        <v>103.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF12" t="n">
         <v>3</v>
       </c>
       <c r="AG12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
         <v>19</v>
@@ -2577,10 +2644,10 @@
         <v>20</v>
       </c>
       <c r="AJ12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
@@ -2592,16 +2659,16 @@
         <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
         <v>22</v>
@@ -2613,7 +2680,7 @@
         <v>9</v>
       </c>
       <c r="AV12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW12" t="n">
         <v>2</v>
@@ -2622,19 +2689,19 @@
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F13" t="n">
         <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>0.449</v>
+        <v>0.442</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
@@ -2681,10 +2748,10 @@
         <v>36.5</v>
       </c>
       <c r="J13" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L13" t="n">
         <v>7.4</v>
@@ -2693,31 +2760,31 @@
         <v>21.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.349</v>
+        <v>0.351</v>
       </c>
       <c r="O13" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P13" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="R13" t="n">
         <v>10.4</v>
       </c>
       <c r="S13" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="T13" t="n">
-        <v>44.8</v>
+        <v>44.6</v>
       </c>
       <c r="U13" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V13" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W13" t="n">
         <v>6.2</v>
@@ -2729,31 +2796,31 @@
         <v>4.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB13" t="n">
         <v>97.09999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF13" t="n">
         <v>20</v>
       </c>
       <c r="AG13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>25</v>
@@ -2762,10 +2829,10 @@
         <v>16</v>
       </c>
       <c r="AK13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
@@ -2774,28 +2841,28 @@
         <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
         <v>6</v>
       </c>
       <c r="AU13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW13" t="n">
         <v>28</v>
@@ -2804,7 +2871,7 @@
         <v>19</v>
       </c>
       <c r="AY13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ13" t="n">
         <v>21</v>
@@ -2816,7 +2883,7 @@
         <v>24</v>
       </c>
       <c r="BC13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -2938,7 +3005,7 @@
         <v>29</v>
       </c>
       <c r="AI14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ14" t="n">
         <v>15</v>
@@ -2959,7 +3026,7 @@
         <v>8</v>
       </c>
       <c r="AP14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ14" t="n">
         <v>28</v>
@@ -2971,7 +3038,7 @@
         <v>10</v>
       </c>
       <c r="AT14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
@@ -2983,7 +3050,7 @@
         <v>14</v>
       </c>
       <c r="AX14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -3042,13 +3109,13 @@
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
         <v>85.59999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
         <v>6.5</v>
@@ -3060,22 +3127,22 @@
         <v>0.345</v>
       </c>
       <c r="O15" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P15" t="n">
         <v>23.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.74</v>
+        <v>0.742</v>
       </c>
       <c r="R15" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S15" t="n">
         <v>32.4</v>
       </c>
       <c r="T15" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U15" t="n">
         <v>20.8</v>
@@ -3093,19 +3160,19 @@
         <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>98.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="AC15" t="n">
         <v>-6.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3123,7 +3190,7 @@
         <v>19</v>
       </c>
       <c r="AJ15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK15" t="n">
         <v>25</v>
@@ -3144,19 +3211,19 @@
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
         <v>9</v>
       </c>
       <c r="AS15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT15" t="n">
         <v>12</v>
       </c>
-      <c r="AT15" t="n">
-        <v>11</v>
-      </c>
       <c r="AU15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV15" t="n">
         <v>5</v>
@@ -3168,7 +3235,7 @@
         <v>20</v>
       </c>
       <c r="AY15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
         <v>20</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -3209,25 +3276,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F16" t="n">
         <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>0.679</v>
+        <v>0.675</v>
       </c>
       <c r="H16" t="n">
         <v>48.6</v>
       </c>
       <c r="I16" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J16" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0.458</v>
@@ -3236,16 +3303,16 @@
         <v>5.2</v>
       </c>
       <c r="M16" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O16" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P16" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q16" t="n">
         <v>0.775</v>
@@ -3257,13 +3324,13 @@
         <v>32.2</v>
       </c>
       <c r="T16" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="U16" t="n">
         <v>21.7</v>
       </c>
       <c r="V16" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W16" t="n">
         <v>8.5</v>
@@ -3272,43 +3339,43 @@
         <v>4.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z16" t="n">
         <v>19.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AD16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF16" t="n">
         <v>4</v>
       </c>
-      <c r="AE16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>3</v>
-      </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
         <v>5</v>
       </c>
       <c r="AI16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3317,7 +3384,7 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>9</v>
@@ -3329,16 +3396,16 @@
         <v>6</v>
       </c>
       <c r="AR16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS16" t="n">
         <v>15</v>
       </c>
       <c r="AT16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV16" t="n">
         <v>6</v>
@@ -3347,22 +3414,22 @@
         <v>7</v>
       </c>
       <c r="AX16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY16" t="n">
         <v>20</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -3469,10 +3536,10 @@
         <v>-2.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF17" t="n">
         <v>20</v>
@@ -3481,7 +3548,7 @@
         <v>20</v>
       </c>
       <c r="AH17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI17" t="n">
         <v>29</v>
@@ -3490,10 +3557,10 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM17" t="n">
         <v>19</v>
@@ -3523,10 +3590,10 @@
         <v>29</v>
       </c>
       <c r="AV17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX17" t="n">
         <v>22</v>
@@ -3538,7 +3605,7 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -3573,25 +3640,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E18" t="n">
         <v>38</v>
       </c>
       <c r="F18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G18" t="n">
-        <v>0.487</v>
+        <v>0.494</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
       </c>
       <c r="I18" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J18" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K18" t="n">
         <v>0.457</v>
@@ -3603,34 +3670,34 @@
         <v>18.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="O18" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P18" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="R18" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S18" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T18" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U18" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V18" t="n">
         <v>16.7</v>
       </c>
       <c r="W18" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="X18" t="n">
         <v>4.9</v>
@@ -3648,10 +3715,10 @@
         <v>97.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3663,7 +3730,7 @@
         <v>16</v>
       </c>
       <c r="AH18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="n">
         <v>17</v>
@@ -3672,7 +3739,7 @@
         <v>26</v>
       </c>
       <c r="AK18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL18" t="n">
         <v>23</v>
@@ -3693,13 +3760,13 @@
         <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS18" t="n">
         <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
@@ -3711,22 +3778,22 @@
         <v>3</v>
       </c>
       <c r="AX18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY18" t="n">
         <v>14</v>
       </c>
       <c r="AZ18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA18" t="n">
         <v>18</v>
       </c>
       <c r="BB18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -3755,28 +3822,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E19" t="n">
         <v>16</v>
       </c>
       <c r="F19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G19" t="n">
-        <v>0.205</v>
+        <v>0.208</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J19" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L19" t="n">
         <v>4.9</v>
@@ -3788,13 +3855,13 @@
         <v>0.332</v>
       </c>
       <c r="O19" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="P19" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.773</v>
+        <v>0.772</v>
       </c>
       <c r="R19" t="n">
         <v>11.7</v>
@@ -3803,16 +3870,16 @@
         <v>29.3</v>
       </c>
       <c r="T19" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U19" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V19" t="n">
         <v>15.1</v>
       </c>
       <c r="W19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X19" t="n">
         <v>3.9</v>
@@ -3821,19 +3888,19 @@
         <v>5.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AA19" t="n">
         <v>21.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-8.6</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3845,16 +3912,16 @@
         <v>29</v>
       </c>
       <c r="AH19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ19" t="n">
         <v>13</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3884,13 +3951,13 @@
         <v>27</v>
       </c>
       <c r="AU19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV19" t="n">
         <v>24</v>
       </c>
       <c r="AW19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX19" t="n">
         <v>28</v>
@@ -3899,13 +3966,13 @@
         <v>26</v>
       </c>
       <c r="AZ19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA19" t="n">
         <v>5</v>
       </c>
       <c r="BB19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC19" t="n">
         <v>28</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -3940,25 +4007,25 @@
         <v>77</v>
       </c>
       <c r="E20" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>0.532</v>
+        <v>0.545</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
       <c r="J20" t="n">
-        <v>82.5</v>
+        <v>82.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
         <v>7.2</v>
@@ -3967,37 +4034,37 @@
         <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="O20" t="n">
         <v>16.5</v>
       </c>
       <c r="P20" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.759</v>
+        <v>0.755</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T20" t="n">
-        <v>43.3</v>
+        <v>43.6</v>
       </c>
       <c r="U20" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V20" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W20" t="n">
         <v>6.7</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
@@ -4006,37 +4073,37 @@
         <v>18.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.09999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
         <v>23</v>
       </c>
       <c r="AI20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AK20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL20" t="n">
         <v>19</v>
@@ -4051,16 +4118,16 @@
         <v>21</v>
       </c>
       <c r="AP20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
         <v>10</v>
       </c>
       <c r="AS20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT20" t="n">
         <v>16</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4090,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -4119,28 +4186,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E21" t="n">
         <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G21" t="n">
-        <v>0.192</v>
+        <v>0.195</v>
       </c>
       <c r="H21" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="J21" t="n">
         <v>82.3</v>
       </c>
       <c r="K21" t="n">
-        <v>0.427</v>
+        <v>0.428</v>
       </c>
       <c r="L21" t="n">
         <v>6.8</v>
@@ -4149,37 +4216,37 @@
         <v>19.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O21" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="P21" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Q21" t="n">
         <v>0.771</v>
       </c>
       <c r="R21" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S21" t="n">
         <v>29.7</v>
       </c>
       <c r="T21" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U21" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V21" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W21" t="n">
         <v>7.1</v>
       </c>
       <c r="X21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y21" t="n">
         <v>4.4</v>
@@ -4191,13 +4258,13 @@
         <v>19</v>
       </c>
       <c r="AB21" t="n">
-        <v>91.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-9.5</v>
+        <v>-9.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4221,7 +4288,7 @@
         <v>28</v>
       </c>
       <c r="AL21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -4379,19 +4446,19 @@
         <v>1.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
       </c>
       <c r="AF22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
         <v>8</v>
@@ -4418,7 +4485,7 @@
         <v>7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -4486,82 +4553,82 @@
         <v>77</v>
       </c>
       <c r="E23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F23" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G23" t="n">
-        <v>0.325</v>
+        <v>0.312</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J23" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
         <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O23" t="n">
         <v>14</v>
       </c>
       <c r="P23" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.732</v>
+        <v>0.73</v>
       </c>
       <c r="R23" t="n">
         <v>9.9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U23" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V23" t="n">
         <v>14.9</v>
       </c>
       <c r="W23" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X23" t="n">
         <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="n">
         <v>18</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.2</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.6</v>
+        <v>-5.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4585,7 +4652,7 @@
         <v>13</v>
       </c>
       <c r="AL23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
@@ -4600,22 +4667,22 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AV23" t="n">
         <v>21</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>20</v>
       </c>
       <c r="AW23" t="n">
         <v>13</v>
@@ -4624,10 +4691,10 @@
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -4665,31 +4732,31 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E24" t="n">
         <v>18</v>
       </c>
       <c r="F24" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G24" t="n">
-        <v>0.228</v>
+        <v>0.231</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>33.6</v>
+        <v>33.7</v>
       </c>
       <c r="J24" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.407</v>
+        <v>0.408</v>
       </c>
       <c r="L24" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M24" t="n">
         <v>26.1</v>
@@ -4698,37 +4765,37 @@
         <v>0.324</v>
       </c>
       <c r="O24" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="P24" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="Q24" t="n">
         <v>0.67</v>
       </c>
       <c r="R24" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S24" t="n">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="T24" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U24" t="n">
         <v>20.5</v>
       </c>
       <c r="V24" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="W24" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z24" t="n">
         <v>21.5</v>
@@ -4740,10 +4807,10 @@
         <v>91.59999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>-9.1</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4761,7 +4828,7 @@
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
@@ -4776,7 +4843,7 @@
         <v>28</v>
       </c>
       <c r="AO24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP24" t="n">
         <v>11</v>
@@ -4785,7 +4852,7 @@
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4803,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY24" t="n">
         <v>27</v>
@@ -4812,7 +4879,7 @@
         <v>25</v>
       </c>
       <c r="BA24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E25" t="n">
         <v>39</v>
       </c>
       <c r="F25" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G25" t="n">
-        <v>0.494</v>
+        <v>0.5</v>
       </c>
       <c r="H25" t="n">
         <v>48.5</v>
@@ -4865,10 +4932,10 @@
         <v>38.9</v>
       </c>
       <c r="J25" t="n">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="K25" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L25" t="n">
         <v>8.6</v>
@@ -4877,7 +4944,7 @@
         <v>25.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="O25" t="n">
         <v>16.5</v>
@@ -4886,16 +4953,16 @@
         <v>21.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.762</v>
+        <v>0.761</v>
       </c>
       <c r="R25" t="n">
         <v>10.9</v>
       </c>
       <c r="S25" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T25" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U25" t="n">
         <v>20.2</v>
@@ -4913,7 +4980,7 @@
         <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AA25" t="n">
         <v>20.4</v>
@@ -4925,7 +4992,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
@@ -4943,10 +5010,10 @@
         <v>5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL25" t="n">
         <v>9</v>
@@ -4955,22 +5022,22 @@
         <v>9</v>
       </c>
       <c r="AN25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR25" t="n">
         <v>14</v>
       </c>
       <c r="AS25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AT25" t="n">
         <v>17</v>
@@ -4991,13 +5058,13 @@
         <v>5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA25" t="n">
         <v>13</v>
       </c>
       <c r="BB25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC25" t="n">
         <v>18</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -5029,19 +5096,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E26" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F26" t="n">
         <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>0.654</v>
+        <v>0.649</v>
       </c>
       <c r="H26" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I26" t="n">
         <v>38.6</v>
@@ -5056,7 +5123,7 @@
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="N26" t="n">
         <v>0.366</v>
@@ -5068,7 +5135,7 @@
         <v>19.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.802</v>
+        <v>0.801</v>
       </c>
       <c r="R26" t="n">
         <v>10.8</v>
@@ -5077,10 +5144,10 @@
         <v>35.3</v>
       </c>
       <c r="T26" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="U26" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V26" t="n">
         <v>13.6</v>
@@ -5098,16 +5165,16 @@
         <v>18.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>103</v>
+        <v>102.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5137,7 +5204,7 @@
         <v>3</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -5167,7 +5234,7 @@
         <v>27</v>
       </c>
       <c r="AX26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5176,10 +5243,10 @@
         <v>2</v>
       </c>
       <c r="BA26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -5211,25 +5278,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E27" t="n">
         <v>27</v>
       </c>
       <c r="F27" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G27" t="n">
-        <v>0.346</v>
+        <v>0.351</v>
       </c>
       <c r="H27" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I27" t="n">
         <v>36.6</v>
       </c>
       <c r="J27" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K27" t="n">
         <v>0.453</v>
@@ -5238,10 +5305,10 @@
         <v>5.6</v>
       </c>
       <c r="M27" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O27" t="n">
         <v>22.2</v>
@@ -5250,28 +5317,28 @@
         <v>28.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="R27" t="n">
         <v>11.1</v>
       </c>
       <c r="S27" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="T27" t="n">
-        <v>44.3</v>
+        <v>44.5</v>
       </c>
       <c r="U27" t="n">
         <v>20.1</v>
       </c>
       <c r="V27" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="W27" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X27" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="n">
         <v>6.3</v>
@@ -5283,13 +5350,13 @@
         <v>23.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.9</v>
+        <v>101.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4</v>
+        <v>-3.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5310,7 +5377,7 @@
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL27" t="n">
         <v>28</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5328,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR27" t="n">
         <v>12</v>
@@ -5337,7 +5404,7 @@
         <v>9</v>
       </c>
       <c r="AT27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU27" t="n">
         <v>28</v>
@@ -5364,7 +5431,7 @@
         <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -5408,28 +5475,28 @@
         <v>48.7</v>
       </c>
       <c r="I28" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J28" t="n">
-        <v>84</v>
+        <v>83.7</v>
       </c>
       <c r="K28" t="n">
         <v>0.466</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.365</v>
+        <v>0.368</v>
       </c>
       <c r="O28" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P28" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q28" t="n">
         <v>0.779</v>
@@ -5441,37 +5508,37 @@
         <v>33.9</v>
       </c>
       <c r="T28" t="n">
-        <v>43.9</v>
+        <v>43.7</v>
       </c>
       <c r="U28" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="V28" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="W28" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.2</v>
+        <v>103</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5489,7 +5556,7 @@
         <v>4</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK28" t="n">
         <v>4</v>
@@ -5501,7 +5568,7 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
         <v>17</v>
@@ -5510,13 +5577,13 @@
         <v>23</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
         <v>14</v>
@@ -5525,7 +5592,7 @@
         <v>4</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
         <v>10</v>
@@ -5540,7 +5607,7 @@
         <v>7</v>
       </c>
       <c r="BA28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -5575,25 +5642,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E29" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F29" t="n">
         <v>32</v>
       </c>
       <c r="G29" t="n">
-        <v>0.59</v>
+        <v>0.584</v>
       </c>
       <c r="H29" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I29" t="n">
         <v>38</v>
       </c>
       <c r="J29" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>0.456</v>
@@ -5602,25 +5669,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="O29" t="n">
         <v>19.6</v>
       </c>
       <c r="P29" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q29" t="n">
         <v>0.787</v>
       </c>
       <c r="R29" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S29" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T29" t="n">
         <v>41.5</v>
@@ -5635,7 +5702,7 @@
         <v>7.5</v>
       </c>
       <c r="X29" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y29" t="n">
         <v>5</v>
@@ -5644,31 +5711,31 @@
         <v>20.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>104.3</v>
+        <v>104.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH29" t="n">
         <v>11</v>
       </c>
       <c r="AI29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ29" t="n">
         <v>14</v>
@@ -5680,7 +5747,7 @@
         <v>8</v>
       </c>
       <c r="AM29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN29" t="n">
         <v>11</v>
@@ -5695,22 +5762,22 @@
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV29" t="n">
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX29" t="n">
         <v>23</v>
@@ -5728,7 +5795,7 @@
         <v>4</v>
       </c>
       <c r="BC29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E30" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F30" t="n">
         <v>42</v>
       </c>
       <c r="G30" t="n">
-        <v>0.462</v>
+        <v>0.455</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
@@ -5781,13 +5848,13 @@
         <v>0.447</v>
       </c>
       <c r="L30" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M30" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="O30" t="n">
         <v>16.9</v>
@@ -5808,43 +5875,43 @@
         <v>43.9</v>
       </c>
       <c r="U30" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V30" t="n">
         <v>15.3</v>
       </c>
       <c r="W30" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X30" t="n">
         <v>6</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z30" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH30" t="n">
         <v>30</v>
@@ -5859,13 +5926,13 @@
         <v>18</v>
       </c>
       <c r="AL30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM30" t="n">
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO30" t="n">
         <v>14</v>
@@ -5880,10 +5947,10 @@
         <v>4</v>
       </c>
       <c r="AS30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU30" t="n">
         <v>30</v>
@@ -5895,10 +5962,10 @@
         <v>17</v>
       </c>
       <c r="AX30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ30" t="n">
         <v>11</v>
@@ -5907,7 +5974,7 @@
         <v>22</v>
       </c>
       <c r="BB30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC30" t="n">
         <v>15</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E31" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F31" t="n">
         <v>33</v>
       </c>
       <c r="G31" t="n">
-        <v>0.577</v>
+        <v>0.571</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J31" t="n">
-        <v>82.3</v>
+        <v>82.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.465</v>
+        <v>0.463</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
@@ -5969,7 +6036,7 @@
         <v>16.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.36</v>
+        <v>0.358</v>
       </c>
       <c r="O31" t="n">
         <v>15.9</v>
@@ -5981,16 +6048,16 @@
         <v>0.742</v>
       </c>
       <c r="R31" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S31" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="T31" t="n">
         <v>44.3</v>
       </c>
       <c r="U31" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="V31" t="n">
         <v>14.9</v>
@@ -6008,16 +6075,16 @@
         <v>20.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.59999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6035,7 +6102,7 @@
         <v>9</v>
       </c>
       <c r="AJ31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK31" t="n">
         <v>5</v>
@@ -6056,13 +6123,13 @@
         <v>22</v>
       </c>
       <c r="AQ31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR31" t="n">
         <v>22</v>
       </c>
-      <c r="AR31" t="n">
-        <v>23</v>
-      </c>
       <c r="AS31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT31" t="n">
         <v>10</v>
@@ -6077,22 +6144,22 @@
         <v>20</v>
       </c>
       <c r="AX31" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AY31" t="n">
         <v>6</v>
       </c>
       <c r="AZ31" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB31" t="n">
         <v>18</v>
       </c>
-      <c r="BA31" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>17</v>
-      </c>
       <c r="BC31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-8-2014-15</t>
+          <t>2015-04-08</t>
         </is>
       </c>
     </row>
